--- a/consent_forms/045_our_special_friendships_health_form--consent_forms.xlsx
+++ b/consent_forms/045_our_special_friendships_health_form--consent_forms.xlsx
@@ -1,15 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="survey" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="choices" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="settings" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="survey" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="choices" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="settings" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -437,12 +437,12 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E22"/>
+  <dimension ref="A1:E21"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="17" customWidth="1" min="1" max="1"/>
-    <col width="25" customWidth="1" min="2" max="2"/>
-    <col width="20" customWidth="1" min="3" max="3"/>
+    <col width="12" customWidth="1" min="1" max="1"/>
+    <col width="38" customWidth="1" min="2" max="2"/>
+    <col width="33" customWidth="1" min="3" max="3"/>
     <col width="6" customWidth="1" min="4" max="4"/>
     <col width="10" customWidth="1" min="5" max="5"/>
   </cols>
@@ -515,17 +515,17 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>note</t>
+          <t>text</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>main_page</t>
+          <t>medical_conditions_page</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Main Page</t>
+          <t>Medical Conditions</t>
         </is>
       </c>
       <c r="D4" t="inlineStr"/>
@@ -538,17 +538,17 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>select_one</t>
+          <t>text</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>family_member_form</t>
+          <t>allergies_page</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>family member</t>
+          <t>Allergies</t>
         </is>
       </c>
       <c r="D5" t="inlineStr"/>
@@ -566,12 +566,12 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>medical_conditions_form</t>
+          <t>special_needs_page</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>medical conditions</t>
+          <t>Special Needs</t>
         </is>
       </c>
       <c r="D6" t="inlineStr"/>
@@ -584,17 +584,17 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>select_multiple</t>
+          <t>select_one</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>special_needs_form</t>
+          <t>doctor_page</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>special needs</t>
+          <t>Doctor</t>
         </is>
       </c>
       <c r="D7" t="inlineStr"/>
@@ -612,12 +612,12 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>allergies_form</t>
+          <t>medical_record_page</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>allergies</t>
+          <t>Medical Record</t>
         </is>
       </c>
       <c r="D8" t="inlineStr"/>
@@ -635,12 +635,12 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>doctor_form</t>
+          <t>doctor_specialties_page</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>doctor's name</t>
+          <t>Doctor's Specialty</t>
         </is>
       </c>
       <c r="D9" t="inlineStr"/>
@@ -658,12 +658,12 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>medical_record_form</t>
+          <t>medical_equipment_page</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>medical record</t>
+          <t>Medical Equipment</t>
         </is>
       </c>
       <c r="D10" t="inlineStr"/>
@@ -681,12 +681,12 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>medical_condition_form</t>
+          <t>medical_insurance_page</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>medical condition</t>
+          <t>Medical Insurance</t>
         </is>
       </c>
       <c r="D11" t="inlineStr"/>
@@ -699,17 +699,17 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>select_one</t>
+          <t>text</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>doctor_form</t>
+          <t>medical_history_page</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>doctor</t>
+          <t>Medical History</t>
         </is>
       </c>
       <c r="D12" t="inlineStr"/>
@@ -722,17 +722,17 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>select_one</t>
+          <t>time</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>doctor_form</t>
+          <t>doctor_visit_frequency_page</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>doctor</t>
+          <t>Doctor Visit Frequency</t>
         </is>
       </c>
       <c r="D13" t="inlineStr"/>
@@ -750,12 +750,12 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>doctor_form</t>
+          <t>doctor_relationship_page</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>doctor</t>
+          <t>Doctor Relationship</t>
         </is>
       </c>
       <c r="D14" t="inlineStr"/>
@@ -768,17 +768,17 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>select_one</t>
+          <t>text</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>doctor_form</t>
+          <t>medical_record_provider_page</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>doctor</t>
+          <t>Medical Record Provider</t>
         </is>
       </c>
       <c r="D15" t="inlineStr"/>
@@ -791,17 +791,17 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>select_one</t>
+          <t>text</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>doctor_form</t>
+          <t>medical_equipment_page_2</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>doctor</t>
+          <t>Medical Equipment Page 2</t>
         </is>
       </c>
       <c r="D16" t="inlineStr"/>
@@ -814,17 +814,17 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>select_one</t>
+          <t>text</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>doctor_form</t>
+          <t>medical_insurance_provider_page</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>doctor</t>
+          <t>Medical Insurance Provider</t>
         </is>
       </c>
       <c r="D17" t="inlineStr"/>
@@ -837,17 +837,17 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>select_one</t>
+          <t>text</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>doctor_form</t>
+          <t>medical_history_page_2</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>doctor</t>
+          <t>Medical History Page 2</t>
         </is>
       </c>
       <c r="D18" t="inlineStr"/>
@@ -860,17 +860,17 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>text</t>
+          <t>time</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>special_needs_form</t>
+          <t>doctor_visit_time_page</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>special needs</t>
+          <t>Doctor Visit Time</t>
         </is>
       </c>
       <c r="D19" t="inlineStr"/>
@@ -883,17 +883,17 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>text</t>
+          <t>time</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>medical_record_form</t>
+          <t>doctor_known_time_page</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>medical record</t>
+          <t>Doctor Known Time</t>
         </is>
       </c>
       <c r="D20" t="inlineStr"/>
@@ -911,39 +911,16 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>allergies_form</t>
+          <t>medical_prescription_medication_page</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>allergies</t>
+          <t>Medical Prescription Medication</t>
         </is>
       </c>
       <c r="D21" t="inlineStr"/>
       <c r="E21" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="22">
-      <c r="A22" t="inlineStr">
-        <is>
-          <t>select_one</t>
-        </is>
-      </c>
-      <c r="B22" t="inlineStr">
-        <is>
-          <t>doctor_form</t>
-        </is>
-      </c>
-      <c r="C22" t="inlineStr">
-        <is>
-          <t>doctor</t>
-        </is>
-      </c>
-      <c r="D22" t="inlineStr"/>
-      <c r="E22" t="inlineStr">
         <is>
           <t>no</t>
         </is>
@@ -960,12 +937,12 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C31"/>
+  <dimension ref="A1:C7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="28" customWidth="1" min="1" max="1"/>
-    <col width="26" customWidth="1" min="2" max="2"/>
-    <col width="26" customWidth="1" min="3" max="3"/>
+    <col width="34" customWidth="1" min="1" max="1"/>
+    <col width="18" customWidth="1" min="2" max="2"/>
+    <col width="18" customWidth="1" min="3" max="3"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -988,510 +965,102 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>family_member_form_choices</t>
+          <t>doctor_page_choices</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>{'name':_'mother'}</t>
+          <t>dr._smith</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>{'name': 'mother'}</t>
+          <t>Dr. Smith</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>family_member_form_choices</t>
+          <t>doctor_page_choices</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>father</t>
+          <t>dr._johnson</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>father</t>
+          <t>Dr. Johnson</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>family_member_form_choices</t>
+          <t>doctor_page_choices</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>mother-in-law</t>
+          <t>dr._brown</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>mother-in-law</t>
+          <t>Dr. Brown</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>family_member_form_choices</t>
+          <t>doctor_relationship_page_choices</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>father-in-law</t>
+          <t>less_than_1_year</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>father-in-law</t>
+          <t>Less than 1 year</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>family_member_form_choices</t>
+          <t>doctor_relationship_page_choices</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>son</t>
+          <t>1-2_years</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>son</t>
+          <t>1-2 years</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>family_member_form_choices</t>
+          <t>doctor_relationship_page_choices</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>daughter</t>
+          <t>2-5_years</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>daughter</t>
-        </is>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" t="inlineStr">
-        <is>
-          <t>family_member_form_choices</t>
-        </is>
-      </c>
-      <c r="B8" t="inlineStr">
-        <is>
-          <t>son-in-law</t>
-        </is>
-      </c>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t>son-in-law</t>
-        </is>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" t="inlineStr">
-        <is>
-          <t>family_member_form_choices</t>
-        </is>
-      </c>
-      <c r="B9" t="inlineStr">
-        <is>
-          <t>daughter-in-law</t>
-        </is>
-      </c>
-      <c r="C9" t="inlineStr">
-        <is>
-          <t>daughter-in-law</t>
-        </is>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" t="inlineStr">
-        <is>
-          <t>special_needs_form_choices</t>
-        </is>
-      </c>
-      <c r="B10" t="inlineStr">
-        <is>
-          <t>{'name':_'wheelchair'}</t>
-        </is>
-      </c>
-      <c r="C10" t="inlineStr">
-        <is>
-          <t>{'name': 'wheelchair'}</t>
-        </is>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" t="inlineStr">
-        <is>
-          <t>special_needs_form_choices</t>
-        </is>
-      </c>
-      <c r="B11" t="inlineStr">
-        <is>
-          <t>{'name':_'guide_dog'}</t>
-        </is>
-      </c>
-      <c r="C11" t="inlineStr">
-        <is>
-          <t>{'name': 'guide dog'}</t>
-        </is>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" t="inlineStr">
-        <is>
-          <t>special_needs_form_choices</t>
-        </is>
-      </c>
-      <c r="B12" t="inlineStr">
-        <is>
-          <t>{'name':_'hearing_aids'}</t>
-        </is>
-      </c>
-      <c r="C12" t="inlineStr">
-        <is>
-          <t>{'name': 'hearing aids'}</t>
-        </is>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" t="inlineStr">
-        <is>
-          <t>doctor_form_choices</t>
-        </is>
-      </c>
-      <c r="B13" t="inlineStr">
-        <is>
-          <t>{'name':_'dr._smith'}</t>
-        </is>
-      </c>
-      <c r="C13" t="inlineStr">
-        <is>
-          <t>{'name': 'Dr. Smith'}</t>
-        </is>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" t="inlineStr">
-        <is>
-          <t>doctor_form_choices</t>
-        </is>
-      </c>
-      <c r="B14" t="inlineStr">
-        <is>
-          <t>{'name':_'dr._johnson'}</t>
-        </is>
-      </c>
-      <c r="C14" t="inlineStr">
-        <is>
-          <t>{'name': 'Dr. Johnson'}</t>
-        </is>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" t="inlineStr">
-        <is>
-          <t>doctor_form_choices</t>
-        </is>
-      </c>
-      <c r="B15" t="inlineStr">
-        <is>
-          <t>{'name':_'dr._brown'}</t>
-        </is>
-      </c>
-      <c r="C15" t="inlineStr">
-        <is>
-          <t>{'name': 'Dr. Brown'}</t>
-        </is>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" t="inlineStr">
-        <is>
-          <t>doctor_form_choices</t>
-        </is>
-      </c>
-      <c r="B16" t="inlineStr">
-        <is>
-          <t>{'name':_'dr._smith'}</t>
-        </is>
-      </c>
-      <c r="C16" t="inlineStr">
-        <is>
-          <t>{'name': 'Dr. Smith'}</t>
-        </is>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" t="inlineStr">
-        <is>
-          <t>doctor_form_choices</t>
-        </is>
-      </c>
-      <c r="B17" t="inlineStr">
-        <is>
-          <t>{'name':_'dr._johnson'}</t>
-        </is>
-      </c>
-      <c r="C17" t="inlineStr">
-        <is>
-          <t>{'name': 'Dr. Johnson'}</t>
-        </is>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18" t="inlineStr">
-        <is>
-          <t>doctor_form_choices</t>
-        </is>
-      </c>
-      <c r="B18" t="inlineStr">
-        <is>
-          <t>{'name':_'dr._brown'}</t>
-        </is>
-      </c>
-      <c r="C18" t="inlineStr">
-        <is>
-          <t>{'name': 'Dr. Brown'}</t>
-        </is>
-      </c>
-    </row>
-    <row r="19">
-      <c r="A19" t="inlineStr">
-        <is>
-          <t>doctor_form_choices</t>
-        </is>
-      </c>
-      <c r="B19" t="inlineStr">
-        <is>
-          <t>{'name':_'dr._smith'}</t>
-        </is>
-      </c>
-      <c r="C19" t="inlineStr">
-        <is>
-          <t>{'name': 'Dr. Smith'}</t>
-        </is>
-      </c>
-    </row>
-    <row r="20">
-      <c r="A20" t="inlineStr">
-        <is>
-          <t>doctor_form_choices</t>
-        </is>
-      </c>
-      <c r="B20" t="inlineStr">
-        <is>
-          <t>{'name':_'dr._johnson'}</t>
-        </is>
-      </c>
-      <c r="C20" t="inlineStr">
-        <is>
-          <t>{'name': 'Dr. Johnson'}</t>
-        </is>
-      </c>
-    </row>
-    <row r="21">
-      <c r="A21" t="inlineStr">
-        <is>
-          <t>doctor_form_choices</t>
-        </is>
-      </c>
-      <c r="B21" t="inlineStr">
-        <is>
-          <t>{'name':_'dr._brown'}</t>
-        </is>
-      </c>
-      <c r="C21" t="inlineStr">
-        <is>
-          <t>{'name': 'Dr. Brown'}</t>
-        </is>
-      </c>
-    </row>
-    <row r="22">
-      <c r="A22" t="inlineStr">
-        <is>
-          <t>doctor_form_choices</t>
-        </is>
-      </c>
-      <c r="B22" t="inlineStr">
-        <is>
-          <t>{'name':_'dr._smith'}</t>
-        </is>
-      </c>
-      <c r="C22" t="inlineStr">
-        <is>
-          <t>{'name': 'Dr. Smith'}</t>
-        </is>
-      </c>
-    </row>
-    <row r="23">
-      <c r="A23" t="inlineStr">
-        <is>
-          <t>doctor_form_choices</t>
-        </is>
-      </c>
-      <c r="B23" t="inlineStr">
-        <is>
-          <t>{'name':_'dr._johnson'}</t>
-        </is>
-      </c>
-      <c r="C23" t="inlineStr">
-        <is>
-          <t>{'name': 'Dr. Johnson'}</t>
-        </is>
-      </c>
-    </row>
-    <row r="24">
-      <c r="A24" t="inlineStr">
-        <is>
-          <t>doctor_form_choices</t>
-        </is>
-      </c>
-      <c r="B24" t="inlineStr">
-        <is>
-          <t>{'name':_'dr._smith'}</t>
-        </is>
-      </c>
-      <c r="C24" t="inlineStr">
-        <is>
-          <t>{'name': 'Dr. Smith'}</t>
-        </is>
-      </c>
-    </row>
-    <row r="25">
-      <c r="A25" t="inlineStr">
-        <is>
-          <t>doctor_form_choices</t>
-        </is>
-      </c>
-      <c r="B25" t="inlineStr">
-        <is>
-          <t>other</t>
-        </is>
-      </c>
-      <c r="C25" t="inlineStr">
-        <is>
-          <t>Other</t>
-        </is>
-      </c>
-    </row>
-    <row r="26">
-      <c r="A26" t="inlineStr">
-        <is>
-          <t>doctor_form_choices</t>
-        </is>
-      </c>
-      <c r="B26" t="inlineStr">
-        <is>
-          <t>yes</t>
-        </is>
-      </c>
-      <c r="C26" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-    </row>
-    <row r="27">
-      <c r="A27" t="inlineStr">
-        <is>
-          <t>doctor_form_choices</t>
-        </is>
-      </c>
-      <c r="B27" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-      <c r="C27" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-    </row>
-    <row r="28">
-      <c r="A28" t="inlineStr">
-        <is>
-          <t>doctor_form_choices</t>
-        </is>
-      </c>
-      <c r="B28" t="inlineStr">
-        <is>
-          <t>yes</t>
-        </is>
-      </c>
-      <c r="C28" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-    </row>
-    <row r="29">
-      <c r="A29" t="inlineStr">
-        <is>
-          <t>doctor_form_choices</t>
-        </is>
-      </c>
-      <c r="B29" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-      <c r="C29" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-    </row>
-    <row r="30">
-      <c r="A30" t="inlineStr">
-        <is>
-          <t>doctor_form_choices</t>
-        </is>
-      </c>
-      <c r="B30" t="inlineStr">
-        <is>
-          <t>yes</t>
-        </is>
-      </c>
-      <c r="C30" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-    </row>
-    <row r="31">
-      <c r="A31" t="inlineStr">
-        <is>
-          <t>doctor_form_choices</t>
-        </is>
-      </c>
-      <c r="B31" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-      <c r="C31" t="inlineStr">
-        <is>
-          <t>No</t>
+          <t>2-5 years</t>
         </is>
       </c>
     </row>
